--- a/excel/agentRole.xlsx
+++ b/excel/agentRole.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>编号</t>
   </si>
@@ -58,6 +58,12 @@
     <t>护甲id</t>
   </si>
   <si>
+    <t>检测范围</t>
+  </si>
+  <si>
+    <t>伤害倍率</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -77,6 +83,12 @@
   </si>
   <si>
     <t>armorId</t>
+  </si>
+  <si>
+    <t>detectRange</t>
+  </si>
+  <si>
+    <t>damageRatio</t>
   </si>
   <si>
     <t>int</t>
@@ -1058,15 +1070,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G608"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:I608"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="25.125" style="2" customWidth="1"/>
     <col min="4" max="7" width="25.125" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="25.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.9916666666667" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:7">
+    <row r="1" ht="16.5" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1088,54 +1102,72 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:7">
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:9">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:7">
+        <v>15</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:9">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1149,12 +1181,18 @@
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="H4" s="3">
+        <v>600</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:9">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1172,8 +1210,14 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="H5" s="3">
+        <v>600</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:9">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1191,8 +1235,14 @@
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="H6" s="3">
+        <v>600</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:9">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1214,8 +1264,14 @@
       <c r="G7" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="H7" s="3">
+        <v>600</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:9">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1237,8 +1293,14 @@
       <c r="G8" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="H8" s="3">
+        <v>600</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:9">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1260,8 +1322,14 @@
       <c r="G9" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="H9" s="3">
+        <v>600</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:9">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1283,8 +1351,14 @@
       <c r="G10" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="H10" s="3">
+        <v>600</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:9">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1298,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F11" s="3">
         <v>3</v>
@@ -1306,8 +1380,14 @@
       <c r="G11" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="H11" s="3">
+        <v>600</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:9">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1315,8 +1395,9 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:9">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1324,8 +1405,9 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:9">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1333,8 +1415,9 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:9">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1342,2168 +1425,2601 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
-    </row>
-    <row r="39" spans="1:3">
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
-    </row>
-    <row r="41" spans="1:3">
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
-    </row>
-    <row r="43" spans="1:3">
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
-    </row>
-    <row r="44" spans="1:3">
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
-    </row>
-    <row r="45" spans="1:3">
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
-    </row>
-    <row r="46" spans="1:3">
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-    </row>
-    <row r="48" spans="1:3">
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-    </row>
-    <row r="49" spans="1:3">
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-    </row>
-    <row r="50" spans="1:3">
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="1:8">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
-    </row>
-    <row r="51" spans="1:3">
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
-    </row>
-    <row r="52" spans="1:3">
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="1:8">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
-    </row>
-    <row r="53" spans="1:3">
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:8">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
-    </row>
-    <row r="54" spans="1:3">
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" spans="1:8">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
-    </row>
-    <row r="55" spans="1:3">
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:8">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
-    </row>
-    <row r="56" spans="1:3">
+      <c r="H55" s="5"/>
+    </row>
+    <row r="56" spans="1:8">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
-    </row>
-    <row r="57" spans="1:3">
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
-    </row>
-    <row r="58" spans="1:3">
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
-    </row>
-    <row r="59" spans="1:3">
+      <c r="H58" s="5"/>
+    </row>
+    <row r="59" spans="1:8">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-    </row>
-    <row r="60" spans="1:3">
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" spans="1:8">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-    </row>
-    <row r="61" spans="1:3">
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-    </row>
-    <row r="62" spans="1:3">
+      <c r="H61" s="5"/>
+    </row>
+    <row r="62" spans="1:8">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
-    </row>
-    <row r="63" spans="1:3">
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" spans="1:8">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-    </row>
-    <row r="64" spans="1:3">
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" spans="1:8">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
-    </row>
-    <row r="65" spans="1:3">
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" spans="1:8">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
-    </row>
-    <row r="66" spans="1:3">
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
-    </row>
-    <row r="67" spans="1:3">
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" spans="1:8">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
-    </row>
-    <row r="68" spans="1:3">
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
-    </row>
-    <row r="69" spans="1:3">
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
-    </row>
-    <row r="70" spans="1:3">
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
-    </row>
-    <row r="72" spans="1:3">
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
-    </row>
-    <row r="73" spans="1:3">
+      <c r="H72" s="5"/>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
-    </row>
-    <row r="74" spans="1:3">
+      <c r="H73" s="5"/>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
-    </row>
-    <row r="75" spans="1:3">
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
-    </row>
-    <row r="76" spans="1:3">
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
-    </row>
-    <row r="77" spans="1:3">
+      <c r="H76" s="5"/>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
-    </row>
-    <row r="78" spans="1:3">
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
-    </row>
-    <row r="79" spans="1:3">
+      <c r="H78" s="5"/>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
-    </row>
-    <row r="80" spans="1:3">
+      <c r="H79" s="5"/>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
-    </row>
-    <row r="81" spans="1:3">
+      <c r="H80" s="5"/>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
-    </row>
-    <row r="82" spans="1:3">
+      <c r="H81" s="5"/>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
-    </row>
-    <row r="83" spans="1:3">
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
-    </row>
-    <row r="84" spans="1:3">
+      <c r="H83" s="5"/>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
-    </row>
-    <row r="86" spans="1:3">
+      <c r="H85" s="5"/>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
-    </row>
-    <row r="87" spans="1:3">
+      <c r="H86" s="5"/>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="H87" s="5"/>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
-    </row>
-    <row r="89" spans="1:3">
+      <c r="H88" s="5"/>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
-    </row>
-    <row r="90" spans="1:3">
+      <c r="H89" s="5"/>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
-    </row>
-    <row r="91" spans="1:3">
+      <c r="H90" s="5"/>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
-    </row>
-    <row r="92" spans="1:3">
+      <c r="H91" s="5"/>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
-    </row>
-    <row r="93" spans="1:3">
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
-    </row>
-    <row r="94" spans="1:3">
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
-    </row>
-    <row r="95" spans="1:3">
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
-    </row>
-    <row r="96" spans="1:3">
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
-    </row>
-    <row r="97" spans="1:3">
+      <c r="H96" s="5"/>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
-    </row>
-    <row r="98" spans="1:3">
+      <c r="H97" s="5"/>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
-    </row>
-    <row r="99" spans="1:3">
+      <c r="H98" s="5"/>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
-    </row>
-    <row r="100" spans="1:3">
+      <c r="H99" s="5"/>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
-    </row>
-    <row r="101" spans="1:3">
+      <c r="H100" s="5"/>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
-    </row>
-    <row r="103" spans="1:3">
+      <c r="H102" s="5"/>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="H103" s="5"/>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
-    </row>
-    <row r="105" spans="1:3">
+      <c r="H104" s="5"/>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
-    </row>
-    <row r="106" spans="1:3">
+      <c r="H105" s="5"/>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
-    </row>
-    <row r="107" spans="1:3">
+      <c r="H106" s="5"/>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
-    </row>
-    <row r="108" spans="1:3">
+      <c r="H107" s="5"/>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
-    </row>
-    <row r="109" spans="1:3">
+      <c r="H108" s="5"/>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
-    </row>
-    <row r="110" spans="1:3">
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
-    </row>
-    <row r="111" spans="1:3">
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
-    </row>
-    <row r="112" spans="1:3">
+      <c r="H111" s="5"/>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
-    </row>
-    <row r="113" spans="1:3">
+      <c r="H112" s="5"/>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
-    </row>
-    <row r="114" spans="1:3">
+      <c r="H113" s="5"/>
+    </row>
+    <row r="114" spans="1:8">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
-    </row>
-    <row r="115" spans="1:3">
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
-    </row>
-    <row r="116" spans="1:3">
+      <c r="H115" s="5"/>
+    </row>
+    <row r="116" spans="1:8">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
-    </row>
-    <row r="117" spans="1:3">
+      <c r="H116" s="5"/>
+    </row>
+    <row r="117" spans="1:8">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
-    </row>
-    <row r="118" spans="1:3">
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="1:8">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
-    </row>
-    <row r="119" spans="1:3">
+      <c r="H118" s="5"/>
+    </row>
+    <row r="119" spans="1:8">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
-    </row>
-    <row r="120" spans="1:3">
+      <c r="H119" s="5"/>
+    </row>
+    <row r="120" spans="1:8">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
-    </row>
-    <row r="121" spans="1:3">
+      <c r="H120" s="5"/>
+    </row>
+    <row r="121" spans="1:8">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
-    </row>
-    <row r="122" spans="1:3">
+      <c r="H121" s="5"/>
+    </row>
+    <row r="122" spans="1:8">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
-    </row>
-    <row r="123" spans="1:3">
+      <c r="H122" s="5"/>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
-    </row>
-    <row r="124" spans="1:3">
+      <c r="H123" s="5"/>
+    </row>
+    <row r="124" spans="1:8">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
-    </row>
-    <row r="125" spans="1:3">
+      <c r="H124" s="5"/>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
-    </row>
-    <row r="126" spans="1:3">
+      <c r="H125" s="5"/>
+    </row>
+    <row r="126" spans="1:8">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
-    </row>
-    <row r="127" spans="1:3">
+      <c r="H126" s="5"/>
+    </row>
+    <row r="127" spans="1:8">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
-    </row>
-    <row r="128" spans="1:3">
+      <c r="H127" s="5"/>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
-    </row>
-    <row r="129" spans="1:3">
+      <c r="H128" s="5"/>
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
-    </row>
-    <row r="130" spans="1:3">
+      <c r="H129" s="5"/>
+    </row>
+    <row r="130" spans="1:8">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
-    </row>
-    <row r="131" spans="1:3">
+      <c r="H130" s="5"/>
+    </row>
+    <row r="131" spans="1:8">
       <c r="A131" s="5"/>
       <c r="B131" s="5"/>
       <c r="C131" s="5"/>
-    </row>
-    <row r="132" spans="1:3">
+      <c r="H131" s="5"/>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="5"/>
       <c r="B132" s="5"/>
       <c r="C132" s="5"/>
-    </row>
-    <row r="133" spans="1:3">
+      <c r="H132" s="5"/>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="5"/>
       <c r="B133" s="5"/>
       <c r="C133" s="5"/>
-    </row>
-    <row r="134" spans="1:3">
+      <c r="H133" s="5"/>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="5"/>
       <c r="B134" s="5"/>
       <c r="C134" s="5"/>
-    </row>
-    <row r="135" spans="1:3">
+      <c r="H134" s="5"/>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="5"/>
       <c r="B135" s="5"/>
       <c r="C135" s="5"/>
-    </row>
-    <row r="136" spans="1:3">
+      <c r="H135" s="5"/>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="5"/>
       <c r="B136" s="5"/>
       <c r="C136" s="5"/>
-    </row>
-    <row r="137" spans="1:3">
+      <c r="H136" s="5"/>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="5"/>
       <c r="B137" s="5"/>
       <c r="C137" s="5"/>
-    </row>
-    <row r="138" spans="1:3">
+      <c r="H137" s="5"/>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="5"/>
       <c r="B138" s="5"/>
       <c r="C138" s="5"/>
-    </row>
-    <row r="139" spans="1:3">
+      <c r="H138" s="5"/>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" s="5"/>
       <c r="B139" s="5"/>
       <c r="C139" s="5"/>
-    </row>
-    <row r="140" spans="1:3">
+      <c r="H139" s="5"/>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="5"/>
       <c r="B140" s="5"/>
       <c r="C140" s="5"/>
-    </row>
-    <row r="141" spans="1:3">
+      <c r="H140" s="5"/>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="5"/>
       <c r="B141" s="5"/>
       <c r="C141" s="5"/>
-    </row>
-    <row r="142" spans="1:3">
+      <c r="H141" s="5"/>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="5"/>
       <c r="B142" s="5"/>
       <c r="C142" s="5"/>
-    </row>
-    <row r="143" spans="1:3">
+      <c r="H142" s="5"/>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="5"/>
       <c r="B143" s="5"/>
       <c r="C143" s="5"/>
-    </row>
-    <row r="144" spans="1:3">
+      <c r="H143" s="5"/>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="5"/>
       <c r="B144" s="5"/>
       <c r="C144" s="5"/>
-    </row>
-    <row r="145" spans="1:3">
+      <c r="H144" s="5"/>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="5"/>
       <c r="B145" s="5"/>
       <c r="C145" s="5"/>
-    </row>
-    <row r="146" spans="1:3">
+      <c r="H145" s="5"/>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" s="5"/>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
-    </row>
-    <row r="147" spans="1:3">
+      <c r="H146" s="5"/>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" s="5"/>
       <c r="B147" s="5"/>
       <c r="C147" s="5"/>
-    </row>
-    <row r="148" spans="1:3">
+      <c r="H147" s="5"/>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" s="5"/>
       <c r="B148" s="5"/>
       <c r="C148" s="5"/>
-    </row>
-    <row r="149" spans="1:3">
+      <c r="H148" s="5"/>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="5"/>
       <c r="B149" s="5"/>
       <c r="C149" s="5"/>
-    </row>
-    <row r="150" spans="1:3">
+      <c r="H149" s="5"/>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" s="5"/>
       <c r="B150" s="5"/>
       <c r="C150" s="5"/>
-    </row>
-    <row r="151" spans="1:3">
+      <c r="H150" s="5"/>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" s="5"/>
       <c r="B151" s="5"/>
       <c r="C151" s="5"/>
-    </row>
-    <row r="152" spans="1:3">
+      <c r="H151" s="5"/>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" s="5"/>
       <c r="B152" s="5"/>
       <c r="C152" s="5"/>
-    </row>
-    <row r="153" spans="1:3">
+      <c r="H152" s="5"/>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" s="5"/>
       <c r="B153" s="5"/>
       <c r="C153" s="5"/>
-    </row>
-    <row r="154" spans="1:3">
+      <c r="H153" s="5"/>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" s="5"/>
       <c r="B154" s="5"/>
       <c r="C154" s="5"/>
-    </row>
-    <row r="155" spans="1:3">
+      <c r="H154" s="5"/>
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155" s="5"/>
       <c r="B155" s="5"/>
       <c r="C155" s="5"/>
-    </row>
-    <row r="156" spans="1:3">
+      <c r="H155" s="5"/>
+    </row>
+    <row r="156" spans="1:8">
       <c r="A156" s="5"/>
       <c r="B156" s="5"/>
       <c r="C156" s="5"/>
-    </row>
-    <row r="157" spans="1:3">
+      <c r="H156" s="5"/>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" s="5"/>
       <c r="B157" s="5"/>
       <c r="C157" s="5"/>
-    </row>
-    <row r="158" spans="1:3">
+      <c r="H157" s="5"/>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158" s="5"/>
       <c r="B158" s="5"/>
       <c r="C158" s="5"/>
-    </row>
-    <row r="159" spans="1:3">
+      <c r="H158" s="5"/>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" s="5"/>
       <c r="B159" s="5"/>
       <c r="C159" s="5"/>
-    </row>
-    <row r="160" spans="1:3">
+      <c r="H159" s="5"/>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" s="5"/>
       <c r="B160" s="5"/>
       <c r="C160" s="5"/>
-    </row>
-    <row r="161" spans="1:3">
+      <c r="H160" s="5"/>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" s="5"/>
       <c r="B161" s="5"/>
       <c r="C161" s="5"/>
-    </row>
-    <row r="162" spans="1:3">
+      <c r="H161" s="5"/>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="5"/>
       <c r="B162" s="5"/>
       <c r="C162" s="5"/>
-    </row>
-    <row r="163" spans="1:3">
+      <c r="H162" s="5"/>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163" s="5"/>
       <c r="B163" s="5"/>
       <c r="C163" s="5"/>
-    </row>
-    <row r="164" spans="1:3">
+      <c r="H163" s="5"/>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" s="5"/>
       <c r="B164" s="5"/>
       <c r="C164" s="5"/>
-    </row>
-    <row r="165" spans="1:3">
+      <c r="H164" s="5"/>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
-    </row>
-    <row r="166" spans="1:3">
+      <c r="H165" s="5"/>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
-    </row>
-    <row r="167" spans="1:3">
+      <c r="H166" s="5"/>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
-    </row>
-    <row r="168" spans="1:3">
+      <c r="H167" s="5"/>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
-    </row>
-    <row r="169" spans="1:3">
+      <c r="H168" s="5"/>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
-    </row>
-    <row r="170" spans="1:3">
+      <c r="H169" s="5"/>
+    </row>
+    <row r="170" spans="1:8">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
-    </row>
-    <row r="171" spans="1:3">
+      <c r="H170" s="5"/>
+    </row>
+    <row r="171" spans="1:8">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
-    </row>
-    <row r="172" spans="1:3">
+      <c r="H171" s="5"/>
+    </row>
+    <row r="172" spans="1:8">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
-    </row>
-    <row r="173" spans="1:3">
+      <c r="H172" s="5"/>
+    </row>
+    <row r="173" spans="1:8">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
-    </row>
-    <row r="174" spans="1:3">
+      <c r="H173" s="5"/>
+    </row>
+    <row r="174" spans="1:8">
       <c r="A174" s="5"/>
       <c r="B174" s="5"/>
       <c r="C174" s="5"/>
-    </row>
-    <row r="175" spans="1:3">
+      <c r="H174" s="5"/>
+    </row>
+    <row r="175" spans="1:8">
       <c r="A175" s="5"/>
       <c r="B175" s="5"/>
       <c r="C175" s="5"/>
-    </row>
-    <row r="176" spans="1:3">
+      <c r="H175" s="5"/>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176" s="5"/>
       <c r="B176" s="5"/>
       <c r="C176" s="5"/>
-    </row>
-    <row r="177" spans="1:3">
+      <c r="H176" s="5"/>
+    </row>
+    <row r="177" spans="1:8">
       <c r="A177" s="5"/>
       <c r="B177" s="5"/>
       <c r="C177" s="5"/>
-    </row>
-    <row r="178" spans="1:3">
+      <c r="H177" s="5"/>
+    </row>
+    <row r="178" spans="1:8">
       <c r="A178" s="5"/>
       <c r="B178" s="5"/>
       <c r="C178" s="5"/>
-    </row>
-    <row r="179" spans="1:3">
+      <c r="H178" s="5"/>
+    </row>
+    <row r="179" spans="1:8">
       <c r="A179" s="5"/>
       <c r="B179" s="5"/>
       <c r="C179" s="5"/>
-    </row>
-    <row r="180" spans="1:3">
+      <c r="H179" s="5"/>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" s="5"/>
       <c r="B180" s="5"/>
       <c r="C180" s="5"/>
-    </row>
-    <row r="181" spans="1:3">
+      <c r="H180" s="5"/>
+    </row>
+    <row r="181" spans="1:8">
       <c r="A181" s="5"/>
       <c r="B181" s="5"/>
       <c r="C181" s="5"/>
-    </row>
-    <row r="182" spans="1:3">
+      <c r="H181" s="5"/>
+    </row>
+    <row r="182" spans="1:8">
       <c r="A182" s="5"/>
       <c r="B182" s="5"/>
       <c r="C182" s="5"/>
-    </row>
-    <row r="183" spans="1:3">
+      <c r="H182" s="5"/>
+    </row>
+    <row r="183" spans="1:8">
       <c r="A183" s="5"/>
       <c r="B183" s="5"/>
       <c r="C183" s="5"/>
-    </row>
-    <row r="184" spans="1:3">
+      <c r="H183" s="5"/>
+    </row>
+    <row r="184" spans="1:8">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
-    </row>
-    <row r="185" spans="1:3">
+      <c r="H184" s="5"/>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
-    </row>
-    <row r="186" spans="1:3">
+      <c r="H185" s="5"/>
+    </row>
+    <row r="186" spans="1:8">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
-    </row>
-    <row r="187" spans="1:3">
+      <c r="H186" s="5"/>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
-    </row>
-    <row r="188" spans="1:3">
+      <c r="H187" s="5"/>
+    </row>
+    <row r="188" spans="1:8">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
-    </row>
-    <row r="189" spans="1:3">
+      <c r="H188" s="5"/>
+    </row>
+    <row r="189" spans="1:8">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
-    </row>
-    <row r="190" spans="1:3">
+      <c r="H189" s="5"/>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
-    </row>
-    <row r="191" spans="1:3">
+      <c r="H190" s="5"/>
+    </row>
+    <row r="191" spans="1:8">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
-    </row>
-    <row r="192" spans="1:3">
+      <c r="H191" s="5"/>
+    </row>
+    <row r="192" spans="1:8">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
-    </row>
-    <row r="193" spans="1:3">
+      <c r="H192" s="5"/>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
-    </row>
-    <row r="194" spans="1:3">
+      <c r="H193" s="5"/>
+    </row>
+    <row r="194" spans="1:8">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
-    </row>
-    <row r="195" spans="1:3">
+      <c r="H194" s="5"/>
+    </row>
+    <row r="195" spans="1:8">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
-    </row>
-    <row r="196" spans="1:3">
+      <c r="H195" s="5"/>
+    </row>
+    <row r="196" spans="1:8">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
-    </row>
-    <row r="197" spans="1:3">
+      <c r="H196" s="5"/>
+    </row>
+    <row r="197" spans="1:8">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
-    </row>
-    <row r="198" spans="1:3">
+      <c r="H197" s="5"/>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
-    </row>
-    <row r="199" spans="1:3">
+      <c r="H198" s="5"/>
+    </row>
+    <row r="199" spans="1:8">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
-    </row>
-    <row r="200" spans="1:3">
+      <c r="H199" s="5"/>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
-    </row>
-    <row r="201" spans="1:3">
+      <c r="H200" s="5"/>
+    </row>
+    <row r="201" spans="1:8">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
-    </row>
-    <row r="202" spans="1:3">
+      <c r="H201" s="5"/>
+    </row>
+    <row r="202" spans="1:8">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
-    </row>
-    <row r="203" spans="1:3">
+      <c r="H202" s="5"/>
+    </row>
+    <row r="203" spans="1:8">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
-    </row>
-    <row r="204" spans="1:3">
+      <c r="H203" s="5"/>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
-    </row>
-    <row r="205" spans="1:3">
+      <c r="H204" s="5"/>
+    </row>
+    <row r="205" spans="1:8">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
-    </row>
-    <row r="206" spans="1:3">
+      <c r="H205" s="5"/>
+    </row>
+    <row r="206" spans="1:8">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
-    </row>
-    <row r="207" spans="1:3">
+      <c r="H206" s="5"/>
+    </row>
+    <row r="207" spans="1:8">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
-    </row>
-    <row r="208" spans="1:3">
+      <c r="H207" s="5"/>
+    </row>
+    <row r="208" spans="1:8">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
-    </row>
-    <row r="209" spans="1:3">
+      <c r="H208" s="5"/>
+    </row>
+    <row r="209" spans="1:8">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
-    </row>
-    <row r="210" spans="1:3">
+      <c r="H209" s="5"/>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
-    </row>
-    <row r="211" spans="1:3">
+      <c r="H210" s="5"/>
+    </row>
+    <row r="211" spans="1:8">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
-    </row>
-    <row r="212" spans="1:3">
+      <c r="H211" s="5"/>
+    </row>
+    <row r="212" spans="1:8">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
-    </row>
-    <row r="213" spans="1:3">
+      <c r="H212" s="5"/>
+    </row>
+    <row r="213" spans="1:8">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
-    </row>
-    <row r="214" spans="1:3">
+      <c r="H213" s="5"/>
+    </row>
+    <row r="214" spans="1:8">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
-    </row>
-    <row r="215" spans="1:3">
+      <c r="H214" s="5"/>
+    </row>
+    <row r="215" spans="1:8">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
-    </row>
-    <row r="216" spans="1:3">
+      <c r="H215" s="5"/>
+    </row>
+    <row r="216" spans="1:8">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
-    </row>
-    <row r="217" spans="1:3">
+      <c r="H216" s="5"/>
+    </row>
+    <row r="217" spans="1:8">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
-    </row>
-    <row r="218" spans="1:3">
+      <c r="H217" s="5"/>
+    </row>
+    <row r="218" spans="1:8">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
-    </row>
-    <row r="219" spans="1:3">
+      <c r="H218" s="5"/>
+    </row>
+    <row r="219" spans="1:8">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
-    </row>
-    <row r="220" spans="1:3">
+      <c r="H219" s="5"/>
+    </row>
+    <row r="220" spans="1:8">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
-    </row>
-    <row r="221" spans="1:3">
+      <c r="H220" s="5"/>
+    </row>
+    <row r="221" spans="1:8">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
-    </row>
-    <row r="222" spans="1:3">
+      <c r="H221" s="5"/>
+    </row>
+    <row r="222" spans="1:8">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
-    </row>
-    <row r="223" spans="1:3">
+      <c r="H222" s="5"/>
+    </row>
+    <row r="223" spans="1:8">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
-    </row>
-    <row r="224" spans="1:3">
+      <c r="H223" s="5"/>
+    </row>
+    <row r="224" spans="1:8">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
-    </row>
-    <row r="225" spans="1:3">
+      <c r="H224" s="5"/>
+    </row>
+    <row r="225" spans="1:8">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
-    </row>
-    <row r="226" spans="1:3">
+      <c r="H225" s="5"/>
+    </row>
+    <row r="226" spans="1:8">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
-    </row>
-    <row r="227" spans="1:3">
+      <c r="H226" s="5"/>
+    </row>
+    <row r="227" spans="1:8">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
-    </row>
-    <row r="228" spans="1:3">
+      <c r="H227" s="5"/>
+    </row>
+    <row r="228" spans="1:8">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
-    </row>
-    <row r="229" spans="1:3">
+      <c r="H228" s="5"/>
+    </row>
+    <row r="229" spans="1:8">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
-    </row>
-    <row r="230" spans="1:3">
+      <c r="H229" s="5"/>
+    </row>
+    <row r="230" spans="1:8">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
-    </row>
-    <row r="231" spans="1:3">
+      <c r="H230" s="5"/>
+    </row>
+    <row r="231" spans="1:8">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
-    </row>
-    <row r="232" spans="1:3">
+      <c r="H231" s="5"/>
+    </row>
+    <row r="232" spans="1:8">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
-    </row>
-    <row r="233" spans="1:3">
+      <c r="H232" s="5"/>
+    </row>
+    <row r="233" spans="1:8">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
-    </row>
-    <row r="234" spans="1:3">
+      <c r="H233" s="5"/>
+    </row>
+    <row r="234" spans="1:8">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
-    </row>
-    <row r="235" spans="1:3">
+      <c r="H234" s="5"/>
+    </row>
+    <row r="235" spans="1:8">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
-    </row>
-    <row r="236" spans="1:3">
+      <c r="H235" s="5"/>
+    </row>
+    <row r="236" spans="1:8">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
-    </row>
-    <row r="237" spans="1:3">
+      <c r="H236" s="5"/>
+    </row>
+    <row r="237" spans="1:8">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
-    </row>
-    <row r="238" spans="1:3">
+      <c r="H237" s="5"/>
+    </row>
+    <row r="238" spans="1:8">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
-    </row>
-    <row r="239" spans="1:3">
+      <c r="H238" s="5"/>
+    </row>
+    <row r="239" spans="1:8">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
-    </row>
-    <row r="240" spans="1:3">
+      <c r="H239" s="5"/>
+    </row>
+    <row r="240" spans="1:8">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
-    </row>
-    <row r="241" spans="1:3">
+      <c r="H240" s="5"/>
+    </row>
+    <row r="241" spans="1:8">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
-    </row>
-    <row r="242" spans="1:3">
+      <c r="H241" s="5"/>
+    </row>
+    <row r="242" spans="1:8">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
-    </row>
-    <row r="243" spans="1:3">
+      <c r="H242" s="5"/>
+    </row>
+    <row r="243" spans="1:8">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
-    </row>
-    <row r="244" spans="1:3">
+      <c r="H243" s="5"/>
+    </row>
+    <row r="244" spans="1:8">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
-    </row>
-    <row r="245" spans="1:3">
+      <c r="H244" s="5"/>
+    </row>
+    <row r="245" spans="1:8">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
-    </row>
-    <row r="246" spans="1:3">
+      <c r="H245" s="5"/>
+    </row>
+    <row r="246" spans="1:8">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
-    </row>
-    <row r="247" spans="1:3">
+      <c r="H246" s="5"/>
+    </row>
+    <row r="247" spans="1:8">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
-    </row>
-    <row r="248" spans="1:3">
+      <c r="H247" s="5"/>
+    </row>
+    <row r="248" spans="1:8">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
-    </row>
-    <row r="249" spans="1:3">
+      <c r="H248" s="5"/>
+    </row>
+    <row r="249" spans="1:8">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
-    </row>
-    <row r="250" spans="1:3">
+      <c r="H249" s="5"/>
+    </row>
+    <row r="250" spans="1:8">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
-    </row>
-    <row r="251" spans="1:3">
+      <c r="H250" s="5"/>
+    </row>
+    <row r="251" spans="1:8">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
-    </row>
-    <row r="252" spans="1:3">
+      <c r="H251" s="5"/>
+    </row>
+    <row r="252" spans="1:8">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
-    </row>
-    <row r="253" spans="1:3">
+      <c r="H252" s="5"/>
+    </row>
+    <row r="253" spans="1:8">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
-    </row>
-    <row r="254" spans="1:3">
+      <c r="H253" s="5"/>
+    </row>
+    <row r="254" spans="1:8">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
-    </row>
-    <row r="255" spans="1:3">
+      <c r="H254" s="5"/>
+    </row>
+    <row r="255" spans="1:8">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
-    </row>
-    <row r="256" spans="1:3">
+      <c r="H255" s="5"/>
+    </row>
+    <row r="256" spans="1:8">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
-    </row>
-    <row r="257" spans="1:3">
+      <c r="H256" s="5"/>
+    </row>
+    <row r="257" spans="1:8">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
-    </row>
-    <row r="258" spans="1:3">
+      <c r="H257" s="5"/>
+    </row>
+    <row r="258" spans="1:8">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
-    </row>
-    <row r="259" spans="1:3">
+      <c r="H258" s="5"/>
+    </row>
+    <row r="259" spans="1:8">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
-    </row>
-    <row r="260" spans="1:3">
+      <c r="H259" s="5"/>
+    </row>
+    <row r="260" spans="1:8">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
-    </row>
-    <row r="261" spans="1:3">
+      <c r="H260" s="5"/>
+    </row>
+    <row r="261" spans="1:8">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
-    </row>
-    <row r="262" spans="1:3">
+      <c r="H261" s="5"/>
+    </row>
+    <row r="262" spans="1:8">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
-    </row>
-    <row r="263" spans="1:3">
+      <c r="H262" s="5"/>
+    </row>
+    <row r="263" spans="1:8">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
-    </row>
-    <row r="264" spans="1:3">
+      <c r="H263" s="5"/>
+    </row>
+    <row r="264" spans="1:8">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
-    </row>
-    <row r="265" spans="1:3">
+      <c r="H264" s="5"/>
+    </row>
+    <row r="265" spans="1:8">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
-    </row>
-    <row r="266" spans="1:3">
+      <c r="H265" s="5"/>
+    </row>
+    <row r="266" spans="1:8">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
-    </row>
-    <row r="267" spans="1:3">
+      <c r="H266" s="5"/>
+    </row>
+    <row r="267" spans="1:8">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
-    </row>
-    <row r="268" spans="1:3">
+      <c r="H267" s="5"/>
+    </row>
+    <row r="268" spans="1:8">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
-    </row>
-    <row r="269" spans="1:3">
+      <c r="H268" s="5"/>
+    </row>
+    <row r="269" spans="1:8">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
-    </row>
-    <row r="270" spans="1:3">
+      <c r="H269" s="5"/>
+    </row>
+    <row r="270" spans="1:8">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
-    </row>
-    <row r="271" spans="1:3">
+      <c r="H270" s="5"/>
+    </row>
+    <row r="271" spans="1:8">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
-    </row>
-    <row r="272" spans="1:3">
+      <c r="H271" s="5"/>
+    </row>
+    <row r="272" spans="1:8">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
-    </row>
-    <row r="273" spans="1:3">
+      <c r="H272" s="5"/>
+    </row>
+    <row r="273" spans="1:8">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
-    </row>
-    <row r="274" spans="1:3">
+      <c r="H273" s="5"/>
+    </row>
+    <row r="274" spans="1:8">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
-    </row>
-    <row r="275" spans="1:3">
+      <c r="H274" s="5"/>
+    </row>
+    <row r="275" spans="1:8">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
-    </row>
-    <row r="276" spans="1:3">
+      <c r="H275" s="5"/>
+    </row>
+    <row r="276" spans="1:8">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
-    </row>
-    <row r="277" spans="1:3">
+      <c r="H276" s="5"/>
+    </row>
+    <row r="277" spans="1:8">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
-    </row>
-    <row r="278" spans="1:3">
+      <c r="H277" s="5"/>
+    </row>
+    <row r="278" spans="1:8">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
-    </row>
-    <row r="279" spans="1:3">
+      <c r="H278" s="5"/>
+    </row>
+    <row r="279" spans="1:8">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
-    </row>
-    <row r="280" spans="1:3">
+      <c r="H279" s="5"/>
+    </row>
+    <row r="280" spans="1:8">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
-    </row>
-    <row r="281" spans="1:3">
+      <c r="H280" s="5"/>
+    </row>
+    <row r="281" spans="1:8">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
-    </row>
-    <row r="282" spans="1:3">
+      <c r="H281" s="5"/>
+    </row>
+    <row r="282" spans="1:8">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
-    </row>
-    <row r="283" spans="1:3">
+      <c r="H282" s="5"/>
+    </row>
+    <row r="283" spans="1:8">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
-    </row>
-    <row r="284" spans="1:3">
+      <c r="H283" s="5"/>
+    </row>
+    <row r="284" spans="1:8">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
-    </row>
-    <row r="285" spans="1:3">
+      <c r="H284" s="5"/>
+    </row>
+    <row r="285" spans="1:8">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
-    </row>
-    <row r="286" spans="1:3">
+      <c r="H285" s="5"/>
+    </row>
+    <row r="286" spans="1:8">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
-    </row>
-    <row r="287" spans="1:3">
+      <c r="H286" s="5"/>
+    </row>
+    <row r="287" spans="1:8">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
-    </row>
-    <row r="288" spans="1:3">
+      <c r="H287" s="5"/>
+    </row>
+    <row r="288" spans="1:8">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
-    </row>
-    <row r="289" spans="1:3">
+      <c r="H288" s="5"/>
+    </row>
+    <row r="289" spans="1:8">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
-    </row>
-    <row r="290" spans="1:3">
+      <c r="H289" s="5"/>
+    </row>
+    <row r="290" spans="1:8">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
-    </row>
-    <row r="291" spans="1:3">
+      <c r="H290" s="5"/>
+    </row>
+    <row r="291" spans="1:8">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
-    </row>
-    <row r="292" spans="1:3">
+      <c r="H291" s="5"/>
+    </row>
+    <row r="292" spans="1:8">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
-    </row>
-    <row r="293" spans="1:3">
+      <c r="H292" s="5"/>
+    </row>
+    <row r="293" spans="1:8">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
-    </row>
-    <row r="294" spans="1:3">
+      <c r="H293" s="5"/>
+    </row>
+    <row r="294" spans="1:8">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
-    </row>
-    <row r="295" spans="1:3">
+      <c r="H294" s="5"/>
+    </row>
+    <row r="295" spans="1:8">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
-    </row>
-    <row r="296" spans="1:3">
+      <c r="H295" s="5"/>
+    </row>
+    <row r="296" spans="1:8">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
-    </row>
-    <row r="297" spans="1:3">
+      <c r="H296" s="5"/>
+    </row>
+    <row r="297" spans="1:8">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
-    </row>
-    <row r="298" spans="1:3">
+      <c r="H297" s="5"/>
+    </row>
+    <row r="298" spans="1:8">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
-    </row>
-    <row r="299" spans="1:3">
+      <c r="H298" s="5"/>
+    </row>
+    <row r="299" spans="1:8">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
-    </row>
-    <row r="300" spans="1:3">
+      <c r="H299" s="5"/>
+    </row>
+    <row r="300" spans="1:8">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
-    </row>
-    <row r="301" spans="1:3">
+      <c r="H300" s="5"/>
+    </row>
+    <row r="301" spans="1:8">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
-    </row>
-    <row r="302" spans="1:3">
+      <c r="H301" s="5"/>
+    </row>
+    <row r="302" spans="1:8">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
-    </row>
-    <row r="303" spans="1:3">
+      <c r="H302" s="5"/>
+    </row>
+    <row r="303" spans="1:8">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
-    </row>
-    <row r="304" spans="1:3">
+      <c r="H303" s="5"/>
+    </row>
+    <row r="304" spans="1:8">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
-    </row>
-    <row r="305" spans="1:3">
+      <c r="H304" s="5"/>
+    </row>
+    <row r="305" spans="1:8">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
-    </row>
-    <row r="306" spans="1:3">
+      <c r="H305" s="5"/>
+    </row>
+    <row r="306" spans="1:8">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
-    </row>
-    <row r="307" spans="1:3">
+      <c r="H306" s="5"/>
+    </row>
+    <row r="307" spans="1:8">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
-    </row>
-    <row r="308" spans="1:3">
+      <c r="H307" s="5"/>
+    </row>
+    <row r="308" spans="1:8">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
-    </row>
-    <row r="309" spans="1:3">
+      <c r="H308" s="5"/>
+    </row>
+    <row r="309" spans="1:8">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
-    </row>
-    <row r="310" spans="1:3">
+      <c r="H309" s="5"/>
+    </row>
+    <row r="310" spans="1:8">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
-    </row>
-    <row r="311" spans="1:3">
+      <c r="H310" s="5"/>
+    </row>
+    <row r="311" spans="1:8">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
-    </row>
-    <row r="312" spans="1:3">
+      <c r="H311" s="5"/>
+    </row>
+    <row r="312" spans="1:8">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
-    </row>
-    <row r="313" spans="1:3">
+      <c r="H312" s="5"/>
+    </row>
+    <row r="313" spans="1:8">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
-    </row>
-    <row r="314" spans="1:3">
+      <c r="H313" s="5"/>
+    </row>
+    <row r="314" spans="1:8">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
-    </row>
-    <row r="315" spans="1:3">
+      <c r="H314" s="5"/>
+    </row>
+    <row r="315" spans="1:8">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
-    </row>
-    <row r="316" spans="1:3">
+      <c r="H315" s="5"/>
+    </row>
+    <row r="316" spans="1:8">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
-    </row>
-    <row r="317" spans="1:3">
+      <c r="H316" s="5"/>
+    </row>
+    <row r="317" spans="1:8">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
-    </row>
-    <row r="318" spans="1:3">
+      <c r="H317" s="5"/>
+    </row>
+    <row r="318" spans="1:8">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
-    </row>
-    <row r="319" spans="1:3">
+      <c r="H318" s="5"/>
+    </row>
+    <row r="319" spans="1:8">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
-    </row>
-    <row r="320" spans="1:3">
+      <c r="H319" s="5"/>
+    </row>
+    <row r="320" spans="1:8">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
-    </row>
-    <row r="321" spans="1:3">
+      <c r="H320" s="5"/>
+    </row>
+    <row r="321" spans="1:8">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
-    </row>
-    <row r="322" spans="1:3">
+      <c r="H321" s="5"/>
+    </row>
+    <row r="322" spans="1:8">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
-    </row>
-    <row r="323" spans="1:3">
+      <c r="H322" s="5"/>
+    </row>
+    <row r="323" spans="1:8">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
-    </row>
-    <row r="324" spans="1:3">
+      <c r="H323" s="5"/>
+    </row>
+    <row r="324" spans="1:8">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
-    </row>
-    <row r="325" spans="1:3">
+      <c r="H324" s="5"/>
+    </row>
+    <row r="325" spans="1:8">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
-    </row>
-    <row r="326" spans="1:3">
+      <c r="H325" s="5"/>
+    </row>
+    <row r="326" spans="1:8">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
-    </row>
-    <row r="327" spans="1:3">
+      <c r="H326" s="5"/>
+    </row>
+    <row r="327" spans="1:8">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
-    </row>
-    <row r="328" spans="1:3">
+      <c r="H327" s="5"/>
+    </row>
+    <row r="328" spans="1:8">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
-    </row>
-    <row r="329" spans="1:3">
+      <c r="H328" s="5"/>
+    </row>
+    <row r="329" spans="1:8">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
-    </row>
-    <row r="330" spans="1:3">
+      <c r="H329" s="5"/>
+    </row>
+    <row r="330" spans="1:8">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
-    </row>
-    <row r="331" spans="1:3">
+      <c r="H330" s="5"/>
+    </row>
+    <row r="331" spans="1:8">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
-    </row>
-    <row r="332" spans="1:3">
+      <c r="H331" s="5"/>
+    </row>
+    <row r="332" spans="1:8">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
-    </row>
-    <row r="333" spans="1:3">
+      <c r="H332" s="5"/>
+    </row>
+    <row r="333" spans="1:8">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
-    </row>
-    <row r="334" spans="1:3">
+      <c r="H333" s="5"/>
+    </row>
+    <row r="334" spans="1:8">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
-    </row>
-    <row r="335" spans="1:3">
+      <c r="H334" s="5"/>
+    </row>
+    <row r="335" spans="1:8">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
-    </row>
-    <row r="336" spans="1:3">
+      <c r="H335" s="5"/>
+    </row>
+    <row r="336" spans="1:8">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
-    </row>
-    <row r="337" spans="1:3">
+      <c r="H336" s="5"/>
+    </row>
+    <row r="337" spans="1:8">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
-    </row>
-    <row r="338" spans="1:3">
+      <c r="H337" s="5"/>
+    </row>
+    <row r="338" spans="1:8">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
-    </row>
-    <row r="339" spans="1:3">
+      <c r="H338" s="5"/>
+    </row>
+    <row r="339" spans="1:8">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
-    </row>
-    <row r="340" spans="1:3">
+      <c r="H339" s="5"/>
+    </row>
+    <row r="340" spans="1:8">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
-    </row>
-    <row r="341" spans="1:3">
+      <c r="H340" s="5"/>
+    </row>
+    <row r="341" spans="1:8">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
-    </row>
-    <row r="342" spans="1:3">
+      <c r="H341" s="5"/>
+    </row>
+    <row r="342" spans="1:8">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
-    </row>
-    <row r="343" spans="1:3">
+      <c r="H342" s="5"/>
+    </row>
+    <row r="343" spans="1:8">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
-    </row>
-    <row r="344" spans="1:3">
+      <c r="H343" s="5"/>
+    </row>
+    <row r="344" spans="1:8">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
-    </row>
-    <row r="345" spans="1:3">
+      <c r="H344" s="5"/>
+    </row>
+    <row r="345" spans="1:8">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
-    </row>
-    <row r="346" spans="1:3">
+      <c r="H345" s="5"/>
+    </row>
+    <row r="346" spans="1:8">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
-    </row>
-    <row r="347" spans="1:3">
+      <c r="H346" s="5"/>
+    </row>
+    <row r="347" spans="1:8">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
-    </row>
-    <row r="348" spans="1:3">
+      <c r="H347" s="5"/>
+    </row>
+    <row r="348" spans="1:8">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
-    </row>
-    <row r="349" spans="1:3">
+      <c r="H348" s="5"/>
+    </row>
+    <row r="349" spans="1:8">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
-    </row>
-    <row r="350" spans="1:3">
+      <c r="H349" s="5"/>
+    </row>
+    <row r="350" spans="1:8">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
-    </row>
-    <row r="351" spans="1:3">
+      <c r="H350" s="5"/>
+    </row>
+    <row r="351" spans="1:8">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
-    </row>
-    <row r="352" spans="1:3">
+      <c r="H351" s="5"/>
+    </row>
+    <row r="352" spans="1:8">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
-    </row>
-    <row r="353" spans="1:3">
+      <c r="H352" s="5"/>
+    </row>
+    <row r="353" spans="1:8">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
-    </row>
-    <row r="354" spans="1:3">
+      <c r="H353" s="5"/>
+    </row>
+    <row r="354" spans="1:8">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
-    </row>
-    <row r="355" spans="1:3">
+      <c r="H354" s="5"/>
+    </row>
+    <row r="355" spans="1:8">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
-    </row>
-    <row r="356" spans="1:3">
+      <c r="H355" s="5"/>
+    </row>
+    <row r="356" spans="1:8">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
-    </row>
-    <row r="357" spans="1:3">
+      <c r="H356" s="5"/>
+    </row>
+    <row r="357" spans="1:8">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
-    </row>
-    <row r="358" spans="1:3">
+      <c r="H357" s="5"/>
+    </row>
+    <row r="358" spans="1:8">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
-    </row>
-    <row r="359" spans="1:3">
+      <c r="H358" s="5"/>
+    </row>
+    <row r="359" spans="1:8">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
-    </row>
-    <row r="360" spans="1:3">
+      <c r="H359" s="5"/>
+    </row>
+    <row r="360" spans="1:8">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
-    </row>
-    <row r="361" spans="1:3">
+      <c r="H360" s="5"/>
+    </row>
+    <row r="361" spans="1:8">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
-    </row>
-    <row r="362" spans="1:3">
+      <c r="H361" s="5"/>
+    </row>
+    <row r="362" spans="1:8">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
-    </row>
-    <row r="363" spans="1:3">
+      <c r="H362" s="5"/>
+    </row>
+    <row r="363" spans="1:8">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
-    </row>
-    <row r="364" spans="1:3">
+      <c r="H363" s="5"/>
+    </row>
+    <row r="364" spans="1:8">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
-    </row>
-    <row r="365" spans="1:3">
+      <c r="H364" s="5"/>
+    </row>
+    <row r="365" spans="1:8">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
-    </row>
-    <row r="366" spans="1:3">
+      <c r="H365" s="5"/>
+    </row>
+    <row r="366" spans="1:8">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
-    </row>
-    <row r="367" spans="1:3">
+      <c r="H366" s="5"/>
+    </row>
+    <row r="367" spans="1:8">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
-    </row>
-    <row r="368" spans="1:3">
+      <c r="H367" s="5"/>
+    </row>
+    <row r="368" spans="1:8">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
-    </row>
-    <row r="369" spans="1:3">
+      <c r="H368" s="5"/>
+    </row>
+    <row r="369" spans="1:8">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
-    </row>
-    <row r="370" spans="1:3">
+      <c r="H369" s="5"/>
+    </row>
+    <row r="370" spans="1:8">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
-    </row>
-    <row r="371" spans="1:3">
+      <c r="H370" s="5"/>
+    </row>
+    <row r="371" spans="1:8">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
-    </row>
-    <row r="372" spans="1:3">
+      <c r="H371" s="5"/>
+    </row>
+    <row r="372" spans="1:8">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
-    </row>
-    <row r="373" spans="1:3">
+      <c r="H372" s="5"/>
+    </row>
+    <row r="373" spans="1:8">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
-    </row>
-    <row r="374" spans="1:3">
+      <c r="H373" s="5"/>
+    </row>
+    <row r="374" spans="1:8">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
-    </row>
-    <row r="375" spans="1:3">
+      <c r="H374" s="5"/>
+    </row>
+    <row r="375" spans="1:8">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
-    </row>
-    <row r="376" spans="1:3">
+      <c r="H375" s="5"/>
+    </row>
+    <row r="376" spans="1:8">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
-    </row>
-    <row r="377" spans="1:3">
+      <c r="H376" s="5"/>
+    </row>
+    <row r="377" spans="1:8">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
-    </row>
-    <row r="378" spans="1:3">
+      <c r="H377" s="5"/>
+    </row>
+    <row r="378" spans="1:8">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
-    </row>
-    <row r="379" spans="1:3">
+      <c r="H378" s="5"/>
+    </row>
+    <row r="379" spans="1:8">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
-    </row>
-    <row r="380" spans="1:3">
+      <c r="H379" s="5"/>
+    </row>
+    <row r="380" spans="1:8">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
-    </row>
-    <row r="381" spans="1:3">
+      <c r="H380" s="5"/>
+    </row>
+    <row r="381" spans="1:8">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
-    </row>
-    <row r="382" spans="1:3">
+      <c r="H381" s="5"/>
+    </row>
+    <row r="382" spans="1:8">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
-    </row>
-    <row r="383" spans="1:3">
+      <c r="H382" s="5"/>
+    </row>
+    <row r="383" spans="1:8">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
-    </row>
-    <row r="384" spans="1:3">
+      <c r="H383" s="5"/>
+    </row>
+    <row r="384" spans="1:8">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
-    </row>
-    <row r="385" spans="1:3">
+      <c r="H384" s="5"/>
+    </row>
+    <row r="385" spans="1:8">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
-    </row>
-    <row r="386" spans="1:3">
+      <c r="H385" s="5"/>
+    </row>
+    <row r="386" spans="1:8">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
-    </row>
-    <row r="387" spans="1:3">
+      <c r="H386" s="5"/>
+    </row>
+    <row r="387" spans="1:8">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
-    </row>
-    <row r="388" spans="1:3">
+      <c r="H387" s="5"/>
+    </row>
+    <row r="388" spans="1:8">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
-    </row>
-    <row r="389" spans="1:3">
+      <c r="H388" s="5"/>
+    </row>
+    <row r="389" spans="1:8">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
-    </row>
-    <row r="390" spans="1:3">
+      <c r="H389" s="5"/>
+    </row>
+    <row r="390" spans="1:8">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
-    </row>
-    <row r="391" spans="1:3">
+      <c r="H390" s="5"/>
+    </row>
+    <row r="391" spans="1:8">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
-    </row>
-    <row r="392" spans="1:3">
+      <c r="H391" s="5"/>
+    </row>
+    <row r="392" spans="1:8">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
-    </row>
-    <row r="393" spans="1:3">
+      <c r="H392" s="5"/>
+    </row>
+    <row r="393" spans="1:8">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
-    </row>
-    <row r="394" spans="1:3">
+      <c r="H393" s="5"/>
+    </row>
+    <row r="394" spans="1:8">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
-    </row>
-    <row r="395" spans="1:3">
+      <c r="H394" s="5"/>
+    </row>
+    <row r="395" spans="1:8">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
-    </row>
-    <row r="396" spans="1:3">
+      <c r="H395" s="5"/>
+    </row>
+    <row r="396" spans="1:8">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
-    </row>
-    <row r="397" spans="1:3">
+      <c r="H396" s="5"/>
+    </row>
+    <row r="397" spans="1:8">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
-    </row>
-    <row r="398" spans="1:3">
+      <c r="H397" s="5"/>
+    </row>
+    <row r="398" spans="1:8">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
-    </row>
-    <row r="399" spans="1:3">
+      <c r="H398" s="5"/>
+    </row>
+    <row r="399" spans="1:8">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
-    </row>
-    <row r="400" spans="1:3">
+      <c r="H399" s="5"/>
+    </row>
+    <row r="400" spans="1:8">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
-    </row>
-    <row r="401" spans="1:3">
+      <c r="H400" s="5"/>
+    </row>
+    <row r="401" spans="1:8">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
-    </row>
-    <row r="402" spans="1:3">
+      <c r="H401" s="5"/>
+    </row>
+    <row r="402" spans="1:8">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
-    </row>
-    <row r="403" spans="1:3">
+      <c r="H402" s="5"/>
+    </row>
+    <row r="403" spans="1:8">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
-    </row>
-    <row r="404" spans="1:3">
+      <c r="H403" s="5"/>
+    </row>
+    <row r="404" spans="1:8">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
-    </row>
-    <row r="405" spans="1:3">
+      <c r="H404" s="5"/>
+    </row>
+    <row r="405" spans="1:8">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
-    </row>
-    <row r="406" spans="1:3">
+      <c r="H405" s="5"/>
+    </row>
+    <row r="406" spans="1:8">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
-    </row>
-    <row r="407" spans="1:3">
+      <c r="H406" s="5"/>
+    </row>
+    <row r="407" spans="1:8">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
-    </row>
-    <row r="408" spans="1:3">
+      <c r="H407" s="5"/>
+    </row>
+    <row r="408" spans="1:8">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
-    </row>
-    <row r="409" spans="1:3">
+      <c r="H408" s="5"/>
+    </row>
+    <row r="409" spans="1:8">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
-    </row>
-    <row r="410" spans="1:3">
+      <c r="H409" s="5"/>
+    </row>
+    <row r="410" spans="1:8">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
-    </row>
-    <row r="411" spans="1:3">
+      <c r="H410" s="5"/>
+    </row>
+    <row r="411" spans="1:8">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
-    </row>
-    <row r="412" spans="1:3">
+      <c r="H411" s="5"/>
+    </row>
+    <row r="412" spans="1:8">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
-    </row>
-    <row r="413" spans="1:3">
+      <c r="H412" s="5"/>
+    </row>
+    <row r="413" spans="1:8">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
-    </row>
-    <row r="414" spans="1:3">
+      <c r="H413" s="5"/>
+    </row>
+    <row r="414" spans="1:8">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
-    </row>
-    <row r="415" spans="1:3">
+      <c r="H414" s="5"/>
+    </row>
+    <row r="415" spans="1:8">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
-    </row>
-    <row r="416" spans="1:3">
+      <c r="H415" s="5"/>
+    </row>
+    <row r="416" spans="1:8">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
-    </row>
-    <row r="417" spans="1:3">
+      <c r="H416" s="5"/>
+    </row>
+    <row r="417" spans="1:8">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
-    </row>
-    <row r="418" spans="1:3">
+      <c r="H417" s="5"/>
+    </row>
+    <row r="418" spans="1:8">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
-    </row>
-    <row r="419" spans="1:3">
+      <c r="H418" s="5"/>
+    </row>
+    <row r="419" spans="1:8">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
-    </row>
-    <row r="420" spans="1:3">
+      <c r="H419" s="5"/>
+    </row>
+    <row r="420" spans="1:8">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
-    </row>
-    <row r="421" spans="1:3">
+      <c r="H420" s="5"/>
+    </row>
+    <row r="421" spans="1:8">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
-    </row>
-    <row r="422" spans="1:3">
+      <c r="H421" s="5"/>
+    </row>
+    <row r="422" spans="1:8">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
-    </row>
-    <row r="423" spans="1:3">
+      <c r="H422" s="5"/>
+    </row>
+    <row r="423" spans="1:8">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
-    </row>
-    <row r="424" spans="1:3">
+      <c r="H423" s="5"/>
+    </row>
+    <row r="424" spans="1:8">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
-    </row>
-    <row r="425" spans="1:3">
+      <c r="H424" s="5"/>
+    </row>
+    <row r="425" spans="1:8">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
-    </row>
-    <row r="426" spans="1:3">
+      <c r="H425" s="5"/>
+    </row>
+    <row r="426" spans="1:8">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
-    </row>
-    <row r="427" spans="1:3">
+      <c r="H426" s="5"/>
+    </row>
+    <row r="427" spans="1:8">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
-    </row>
-    <row r="428" spans="1:3">
+      <c r="H427" s="5"/>
+    </row>
+    <row r="428" spans="1:8">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
-    </row>
-    <row r="429" spans="1:3">
+      <c r="H428" s="5"/>
+    </row>
+    <row r="429" spans="1:8">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
-    </row>
-    <row r="430" spans="1:3">
+      <c r="H429" s="5"/>
+    </row>
+    <row r="430" spans="1:8">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
-    </row>
-    <row r="431" spans="1:3">
+      <c r="H430" s="5"/>
+    </row>
+    <row r="431" spans="1:8">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
-    </row>
-    <row r="432" spans="1:3">
+      <c r="H431" s="5"/>
+    </row>
+    <row r="432" spans="1:8">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
-    </row>
-    <row r="433" spans="1:3">
+      <c r="H432" s="5"/>
+    </row>
+    <row r="433" spans="1:8">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
-    </row>
-    <row r="434" spans="1:3">
+      <c r="H433" s="5"/>
+    </row>
+    <row r="434" spans="1:8">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
-    </row>
-    <row r="435" spans="1:3">
+      <c r="H434" s="5"/>
+    </row>
+    <row r="435" spans="1:8">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
-    </row>
-    <row r="436" spans="1:3">
+      <c r="H435" s="5"/>
+    </row>
+    <row r="436" spans="1:8">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
-    </row>
-    <row r="437" spans="1:3">
+      <c r="H436" s="5"/>
+    </row>
+    <row r="437" spans="1:8">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
-    </row>
-    <row r="438" spans="1:3">
+      <c r="H437" s="5"/>
+    </row>
+    <row r="438" spans="1:8">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
-    </row>
-    <row r="439" spans="1:3">
+      <c r="H438" s="5"/>
+    </row>
+    <row r="439" spans="1:8">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
-    </row>
-    <row r="440" spans="1:3">
+      <c r="H439" s="5"/>
+    </row>
+    <row r="440" spans="1:8">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
-    </row>
-    <row r="441" spans="1:3">
+      <c r="H440" s="5"/>
+    </row>
+    <row r="441" spans="1:8">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
-    </row>
-    <row r="442" spans="1:3">
+      <c r="H441" s="5"/>
+    </row>
+    <row r="442" spans="1:8">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
-    </row>
-    <row r="443" spans="1:3">
+      <c r="H442" s="5"/>
+    </row>
+    <row r="443" spans="1:8">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
-    </row>
-    <row r="444" spans="1:3">
+      <c r="H443" s="5"/>
+    </row>
+    <row r="444" spans="1:8">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
-    </row>
-    <row r="445" spans="1:3">
+      <c r="H444" s="5"/>
+    </row>
+    <row r="445" spans="1:8">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
-    </row>
-    <row r="446" spans="1:3">
+      <c r="H445" s="5"/>
+    </row>
+    <row r="446" spans="1:8">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
-    </row>
-    <row r="447" spans="1:3">
+      <c r="H446" s="5"/>
+    </row>
+    <row r="447" spans="1:8">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
-    </row>
-    <row r="448" spans="1:3">
+      <c r="H447" s="5"/>
+    </row>
+    <row r="448" spans="1:8">
       <c r="A448" s="5"/>
     </row>
     <row r="449" spans="1:1">

--- a/excel/agentRole.xlsx
+++ b/excel/agentRole.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>编号</t>
   </si>
@@ -64,6 +64,9 @@
     <t>伤害倍率</t>
   </si>
   <si>
+    <t>攻击间隔倍率</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -89,6 +92,9 @@
   </si>
   <si>
     <t>damageRatio</t>
+  </si>
+  <si>
+    <t>attackIntervalRatio</t>
   </si>
   <si>
     <t>int</t>
@@ -1070,17 +1076,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I608"/>
+  <dimension ref="A1:J608"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="25.125" style="2" customWidth="1"/>
     <col min="4" max="7" width="25.125" style="3" customWidth="1"/>
     <col min="8" max="8" width="25.125" style="2" customWidth="1"/>
     <col min="9" max="9" width="19.9916666666667" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="10" max="10" width="17.1666666666667" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:9">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1108,66 +1115,75 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:9">
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:9">
+        <v>18</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:9">
+        <v>20</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:10">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -1191,8 +1207,11 @@
       <c r="I4" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:9">
+      <c r="J4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:10">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -1216,8 +1235,11 @@
       <c r="I5" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:9">
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:10">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -1241,8 +1263,11 @@
       <c r="I6" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:9">
+      <c r="J6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:10">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -1270,8 +1295,11 @@
       <c r="I7" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:9">
+      <c r="J7" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:10">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -1299,8 +1327,11 @@
       <c r="I8" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:9">
+      <c r="J8" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:10">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -1328,8 +1359,11 @@
       <c r="I9" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:9">
+      <c r="J9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:10">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -1357,8 +1391,11 @@
       <c r="I10" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:9">
+      <c r="J10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:10">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -1386,8 +1423,11 @@
       <c r="I11" s="1">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:9">
+      <c r="J11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1397,7 +1437,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:9">
+    <row r="13" s="1" customFormat="1" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1407,7 +1447,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:9">
+    <row r="14" s="1" customFormat="1" spans="1:10">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1417,7 +1457,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:9">
+    <row r="15" s="1" customFormat="1" spans="1:10">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1427,7 +1467,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>

--- a/excel/agentRole.xlsx
+++ b/excel/agentRole.xlsx
@@ -32,6 +32,38 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+控制难度的类型</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -110,7 +142,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +299,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1219,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3">
         <v>0</v>
@@ -1247,7 +1290,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -1307,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
@@ -1339,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>0</v>
@@ -1403,7 +1446,7 @@
         <v>2</v>
       </c>
       <c r="C11" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3">
         <v>0</v>
@@ -4549,5 +4592,6 @@
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>